--- a/assets/constructions/examples/ctd_inserts_plungturning.xlsx
+++ b/assets/constructions/examples/ctd_inserts_plungturning.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO3"/>
+  <dimension ref="A1:AT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,64 +634,93 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MABL 3 020          1025</t>
+          <t>NP2002RK TN6025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CoroCut® XS</t>
+          <t>TopGroove</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CoroCut XS -size 3L</t>
+          <t>2_NG</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PMKNS</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>PMS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>KNH</t>
+        </is>
+      </c>
       <c r="H2" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>3.175</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>3.68</v>
+      </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -702,7 +731,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>COR_XS:3L</t>
+          <t>WIDIA_N02</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -714,7 +743,7 @@
         <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y2" t="n">
         <v>4</v>
@@ -724,22 +753,22 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>TN6025</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>MABL 3 020</t>
+          <t>NP2002RK</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>MABL 3</t>
+          <t>NP2002</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>PVD TIALN+TIN</t>
+          <t>X PVD</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -747,11 +776,7 @@
           <t>PVD</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>HC</t>
-        </is>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>1</v>
       </c>
@@ -765,88 +790,91 @@
           <t>VHM</t>
         </is>
       </c>
-      <c r="AJ2" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
-      <c r="AM2" t="n">
-        <v>0.005</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2020 / Coromant Web-site</t>
+          <t>2017 / WIDIA Catalog</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NP2002RK TN6025</t>
+          <t>MABL 3 020          1025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TopGroove</t>
+          <t>CoroCut® XS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2_NG</t>
+          <t>CoroCut XS -size 3L</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PMS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>KNH</t>
-        </is>
-      </c>
+          <t>PMKNS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>3.175</v>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>3.68</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -857,7 +885,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>WIDIA_N02</t>
+          <t>COR_XS:3L</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +897,7 @@
         <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
         <v>4</v>
@@ -879,22 +907,22 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>TN6025</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>NP2002RK</t>
+          <t>MABL 3 020</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>NP2002</t>
+          <t>MABL 3</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>X PVD</t>
+          <t>PVD TIALN+TIN</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -902,7 +930,11 @@
           <t>PVD</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
       <c r="AG3" t="b">
         <v>1</v>
       </c>
@@ -916,20 +948,35 @@
           <t>VHM</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AJ3" t="b">
+        <v>0</v>
+      </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
-      <c r="AM3" t="inlineStr"/>
+      <c r="AM3" t="n">
+        <v>0.005</v>
+      </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2017 / WIDIA Catalog</t>
+          <t>2020 / Coromant Web-site</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
